--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>87</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.90e+05</t>
-  </si>
-  <si>
-    <t>(74667.065)</t>
-  </si>
-  <si>
-    <t>497.771</t>
-  </si>
-  <si>
-    <t>(32.825)</t>
-  </si>
-  <si>
-    <t>3.574</t>
-  </si>
-  <si>
-    <t>(0.042)</t>
-  </si>
-  <si>
-    <t>11.511</t>
-  </si>
-  <si>
-    <t>(1.706)</t>
-  </si>
-  <si>
-    <t>88.887</t>
-  </si>
-  <si>
-    <t>(0.428)</t>
-  </si>
-  <si>
-    <t>1.10e+06</t>
-  </si>
-  <si>
-    <t>(51124.498)</t>
-  </si>
-  <si>
-    <t>2.617</t>
-  </si>
-  <si>
-    <t>(0.116)</t>
-  </si>
-  <si>
-    <t>3.534</t>
-  </si>
-  <si>
-    <t>(0.406)</t>
-  </si>
-  <si>
-    <t>34.170</t>
-  </si>
-  <si>
-    <t>(3.139)</t>
-  </si>
-  <si>
-    <t>0.977</t>
-  </si>
-  <si>
-    <t>(0.016)</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.42e+05</t>
-  </si>
-  <si>
-    <t>(1.41e+05)</t>
-  </si>
-  <si>
-    <t>488.961</t>
-  </si>
-  <si>
-    <t>(68.175)</t>
-  </si>
-  <si>
-    <t>3.286</t>
-  </si>
-  <si>
-    <t>(0.075)</t>
-  </si>
-  <si>
-    <t>32.538</t>
-  </si>
-  <si>
-    <t>(5.528)</t>
-  </si>
-  <si>
-    <t>91.342</t>
-  </si>
-  <si>
-    <t>(0.636)</t>
-  </si>
-  <si>
-    <t>1.36e+06</t>
-  </si>
-  <si>
-    <t>(94774.014)</t>
-  </si>
-  <si>
-    <t>3.464</t>
-  </si>
-  <si>
-    <t>(0.195)</t>
-  </si>
-  <si>
-    <t>7.077</t>
-  </si>
-  <si>
-    <t>(0.786)</t>
-  </si>
-  <si>
-    <t>49.423</t>
-  </si>
-  <si>
-    <t>(4.325)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>113</t>
+    <t>116</t>
+  </si>
+  <si>
+    <t>115</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.52e+05</t>
-  </si>
-  <si>
-    <t>-8.810</t>
-  </si>
-  <si>
-    <t>-0.288***</t>
-  </si>
-  <si>
-    <t>21.027***</t>
-  </si>
-  <si>
-    <t>2.455***</t>
-  </si>
-  <si>
-    <t>2.64e+05**</t>
-  </si>
-  <si>
-    <t>0.847***</t>
-  </si>
-  <si>
-    <t>3.543***</t>
-  </si>
-  <si>
-    <t>15.253**</t>
-  </si>
-  <si>
-    <t>0.023</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T3_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2018_T3_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>88</t>
+  </si>
+  <si>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.90e+05</t>
+  </si>
+  <si>
+    <t>(74667.065)</t>
+  </si>
+  <si>
+    <t>497.771</t>
+  </si>
+  <si>
+    <t>(32.825)</t>
+  </si>
+  <si>
+    <t>3.574</t>
+  </si>
+  <si>
+    <t>(0.042)</t>
+  </si>
+  <si>
+    <t>11.511</t>
+  </si>
+  <si>
+    <t>(1.706)</t>
+  </si>
+  <si>
+    <t>88.887</t>
+  </si>
+  <si>
+    <t>(0.428)</t>
+  </si>
+  <si>
+    <t>1.10e+06</t>
+  </si>
+  <si>
+    <t>(51124.498)</t>
+  </si>
+  <si>
+    <t>2.617</t>
+  </si>
+  <si>
+    <t>(0.116)</t>
+  </si>
+  <si>
+    <t>3.534</t>
+  </si>
+  <si>
+    <t>(0.406)</t>
+  </si>
+  <si>
+    <t>34.170</t>
+  </si>
+  <si>
+    <t>(3.139)</t>
+  </si>
+  <si>
+    <t>0.977</t>
+  </si>
+  <si>
+    <t>(0.016)</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>7.42e+05</t>
+  </si>
+  <si>
+    <t>(1.41e+05)</t>
+  </si>
+  <si>
+    <t>488.961</t>
+  </si>
+  <si>
+    <t>(68.175)</t>
+  </si>
+  <si>
+    <t>3.286</t>
+  </si>
+  <si>
+    <t>(0.075)</t>
+  </si>
+  <si>
+    <t>32.538</t>
+  </si>
+  <si>
+    <t>(5.528)</t>
+  </si>
+  <si>
+    <t>91.342</t>
+  </si>
+  <si>
+    <t>(0.636)</t>
+  </si>
+  <si>
+    <t>1.36e+06</t>
+  </si>
+  <si>
+    <t>(94774.014)</t>
+  </si>
+  <si>
+    <t>3.464</t>
+  </si>
+  <si>
+    <t>(0.195)</t>
+  </si>
+  <si>
+    <t>7.077</t>
+  </si>
+  <si>
+    <t>(0.786)</t>
+  </si>
+  <si>
+    <t>49.423</t>
+  </si>
+  <si>
+    <t>(4.325)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -201,10 +201,10 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>115</t>
+    <t>114</t>
+  </si>
+  <si>
+    <t>113</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.52e+05</t>
+  </si>
+  <si>
+    <t>-8.810</t>
+  </si>
+  <si>
+    <t>-0.288***</t>
+  </si>
+  <si>
+    <t>21.027***</t>
+  </si>
+  <si>
+    <t>2.455***</t>
+  </si>
+  <si>
+    <t>2.64e+05**</t>
+  </si>
+  <si>
+    <t>0.847***</t>
+  </si>
+  <si>
+    <t>3.543***</t>
+  </si>
+  <si>
+    <t>15.253**</t>
+  </si>
+  <si>
+    <t>0.023</t>
   </si>
 </sst>
 </file>
